--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_TU SUPER CB LA ZUBIA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_TU SUPER CB LA ZUBIA.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ CANTERO</t>
+          <t>D. GARCÍA GAZQUEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
-        <v>72.25709999999999</v>
+        <v>50.4121</v>
       </c>
       <c r="E2" t="n">
-        <v>56.7291</v>
+        <v>50.4121</v>
       </c>
       <c r="F2" t="n">
-        <v>15.5277</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>32.0707</v>
+        <v>50.4121</v>
       </c>
       <c r="H2" t="n">
-        <v>25.8022</v>
+        <v>20.2787</v>
       </c>
       <c r="I2" t="n">
-        <v>6.2685</v>
+        <v>30.1333</v>
       </c>
       <c r="J2" t="n">
-        <v>58.1429</v>
+        <v>50.4121</v>
       </c>
       <c r="K2" t="n">
-        <v>42.2584</v>
+        <v>20.2787</v>
       </c>
       <c r="L2" t="n">
-        <v>15.8843</v>
+        <v>30.1333</v>
       </c>
       <c r="M2" t="n">
-        <v>-26.0722</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-16.4565</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-9.6157</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-26.1656</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-61.2508</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>35.0854</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>60.9713</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>34.3823</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>26.5889</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>5.3809</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>25.4551</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-20.0743</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. GARCÍA GAZQUEZ</t>
+          <t>J. RODRIGUEZ CANTERO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>50.4121</v>
+        <v>37.047</v>
       </c>
       <c r="E3" t="n">
-        <v>50.4121</v>
+        <v>34.0648</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2.982599999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>50.4121</v>
+        <v>32.0707</v>
       </c>
       <c r="H3" t="n">
-        <v>20.2787</v>
+        <v>25.8022</v>
       </c>
       <c r="I3" t="n">
-        <v>30.1333</v>
+        <v>6.2685</v>
       </c>
       <c r="J3" t="n">
-        <v>50.4121</v>
+        <v>58.1429</v>
       </c>
       <c r="K3" t="n">
-        <v>20.2787</v>
+        <v>42.2584</v>
       </c>
       <c r="L3" t="n">
-        <v>30.1333</v>
+        <v>15.8843</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-26.0722</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-16.4565</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-9.6157</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-26.1656</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-61.2508</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>35.0854</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>25.761</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>11.7176</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>14.0432</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>5.3809</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>25.4551</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-20.0743</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>5.291900000000002</v>
+        <v>13.9595</v>
       </c>
       <c r="E4" t="n">
-        <v>24.6177</v>
+        <v>30.2888</v>
       </c>
       <c r="F4" t="n">
-        <v>-19.326</v>
+        <v>-16.3302</v>
       </c>
       <c r="G4" t="n">
         <v>19.8944</v>
@@ -766,13 +766,13 @@
         <v>24.1829</v>
       </c>
       <c r="S4" t="n">
-        <v>-9.196300000000001</v>
+        <v>-0.5288999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-5.7318</v>
+        <v>-0.06029999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-3.4645</v>
+        <v>-0.4685999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>-7.1903</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. AMAYA QUINTERO</t>
+          <t>M. WILHELMI MARTINEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3601000000000001</v>
+        <v>0.4213</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.2159</v>
+        <v>0.0596</v>
       </c>
       <c r="F5" t="n">
-        <v>3.576</v>
+        <v>0.3617</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7654999999999998</v>
+        <v>0.0901</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6437</v>
+        <v>-0.1816</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8782000000000001</v>
+        <v>0.2717</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.392</v>
+        <v>0.0202</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0031</v>
+        <v>0.0202</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.3951</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.1575</v>
+        <v>0.0699</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6405999999999999</v>
+        <v>-0.2018</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5169</v>
+        <v>0.2717</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7929</v>
+        <v>0.1982</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.7663</v>
+        <v>0.1982</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9493</v>
+        <v>0.1331</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5568</v>
+        <v>0.0395</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6074999999999999</v>
+        <v>0.0936</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.1477</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.4074</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.7403</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. WILHELMI MARTINEZ</t>
+          <t>A. SANCHEZ BARRERA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2633</v>
+        <v>-0.6873</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0422</v>
+        <v>-0.8663</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3055</v>
+        <v>0.1791</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0901</v>
+        <v>-0.7451</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1816</v>
+        <v>-0.7451</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2717</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0202</v>
+        <v>-0.6791</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0202</v>
+        <v>-0.6791</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0699</v>
+        <v>-0.066</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2018</v>
+        <v>-0.066</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2717</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0.1982</v>
@@ -922,13 +922,13 @@
         <v>0.1982</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.025</v>
+        <v>-0.1404</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0624</v>
+        <v>-0.1872</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0374</v>
+        <v>0.0468</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. SANCHEZ BARRERA</t>
+          <t>S. AMAYA QUINTERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7153</v>
+        <v>-0.8746999999999998</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8663</v>
+        <v>-4.619199999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.151</v>
+        <v>3.7445</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7451</v>
+        <v>0.7654999999999998</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7451</v>
+        <v>1.6437</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-0.8782000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6791</v>
+        <v>-1.392</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6791</v>
+        <v>1.0031</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-2.3951</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.066</v>
+        <v>2.1575</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.066</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.5169</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1982</v>
+        <v>0.7929</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1982</v>
+        <v>3.7663</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1685</v>
+        <v>-0.2854</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1872</v>
+        <v>0.1536000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0187</v>
+        <v>-0.4390000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-2.1477</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.4074</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.7403</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9649</v>
+        <v>-1.0105</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1955</v>
+        <v>-0.2973</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7694</v>
+        <v>-0.7131999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>-2.3584</v>
@@ -1078,13 +1078,13 @@
         <v>0.1982</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5917</v>
+        <v>0.5461</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4919</v>
+        <v>0.3901</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0998</v>
+        <v>0.156</v>
       </c>
       <c r="V8" t="n">
         <v>0.6036</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. CAMARA FERNANDEZ</t>
+          <t>H. TAVIO SOLIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2105</v>
+        <v>-1.028100000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.5277</v>
+        <v>11.0797</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3171</v>
+        <v>-12.1075</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.8278</v>
+        <v>4.308800000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4695</v>
+        <v>-3.1832</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3583</v>
+        <v>7.491700000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.0374</v>
+        <v>19.8694</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6791</v>
+        <v>5.255</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3583</v>
+        <v>14.6144</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2096</v>
+        <v>-15.5606</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2096</v>
+        <v>-8.437799999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-7.1226</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3964</v>
+        <v>8.1272</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9911</v>
+        <v>-8.9199</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5947</v>
+        <v>17.0471</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9863</v>
+        <v>-4.105700000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4992</v>
+        <v>-3.5465</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4871</v>
+        <v>-0.5593000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-9.358000000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.6766</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-13.0347</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.411399999999999</v>
+        <v>-2.2385</v>
       </c>
       <c r="E10" t="n">
-        <v>9.4276</v>
+        <v>6.321700000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-12.8394</v>
+        <v>-8.5608</v>
       </c>
       <c r="G10" t="n">
         <v>12.2414</v>
@@ -1234,13 +1234,13 @@
         <v>32.5087</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.9932</v>
+        <v>-1.8204</v>
       </c>
       <c r="T10" t="n">
-        <v>4.3937</v>
+        <v>1.2878</v>
       </c>
       <c r="U10" t="n">
-        <v>-7.3871</v>
+        <v>-3.1085</v>
       </c>
       <c r="V10" t="n">
         <v>-12.6595</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. WRIGHT RODRIGUEZ</t>
+          <t>L. CAMARA FERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.3302</v>
+        <v>-3.1263</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.806000000000001</v>
+        <v>-3.5277</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5239999999999996</v>
+        <v>0.4014</v>
       </c>
       <c r="G11" t="n">
-        <v>8.9924</v>
+        <v>-1.8278</v>
       </c>
       <c r="H11" t="n">
-        <v>1.0792</v>
+        <v>-0.4695</v>
       </c>
       <c r="I11" t="n">
-        <v>7.912999999999999</v>
+        <v>-1.3583</v>
       </c>
       <c r="J11" t="n">
-        <v>25.7403</v>
+        <v>-2.0374</v>
       </c>
       <c r="K11" t="n">
-        <v>12.7991</v>
+        <v>-0.6791</v>
       </c>
       <c r="L11" t="n">
-        <v>12.9412</v>
+        <v>-1.3583</v>
       </c>
       <c r="M11" t="n">
-        <v>-16.7478</v>
+        <v>0.2096</v>
       </c>
       <c r="N11" t="n">
-        <v>-11.7197</v>
+        <v>0.2096</v>
       </c>
       <c r="O11" t="n">
-        <v>-5.0284</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-8.1272</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q11" t="n">
-        <v>-35.4818</v>
+        <v>-0.9911</v>
       </c>
       <c r="R11" t="n">
-        <v>27.3548</v>
+        <v>0.5947</v>
       </c>
       <c r="S11" t="n">
-        <v>14.9221</v>
+        <v>-0.9021</v>
       </c>
       <c r="T11" t="n">
-        <v>7.058</v>
+        <v>-0.4992</v>
       </c>
       <c r="U11" t="n">
-        <v>7.8641</v>
+        <v>-0.4029</v>
       </c>
       <c r="V11" t="n">
-        <v>-21.1175</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-2.1225</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-18.995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.2744</v>
+        <v>-7.8742</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2227</v>
+        <v>-3.0189</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.0517</v>
+        <v>-4.8553</v>
       </c>
       <c r="G12" t="n">
         <v>-1.1155</v>
@@ -1390,13 +1390,13 @@
         <v>0.9911</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3682</v>
+        <v>0.0322</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1321</v>
+        <v>0.07170000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2362</v>
+        <v>-0.0396</v>
       </c>
       <c r="V12" t="n">
         <v>-3.8175</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>H. TAVIO SOLIS</t>
+          <t>F. SERRANO RUBIO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.0436</v>
+        <v>-12.8064</v>
       </c>
       <c r="E13" t="n">
-        <v>5.674100000000001</v>
+        <v>-2.16</v>
       </c>
       <c r="F13" t="n">
-        <v>-16.7176</v>
+        <v>-10.6462</v>
       </c>
       <c r="G13" t="n">
-        <v>4.308800000000001</v>
+        <v>-6.830699999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.1832</v>
+        <v>-2.3772</v>
       </c>
       <c r="I13" t="n">
-        <v>7.491700000000001</v>
+        <v>-4.453499999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>19.8694</v>
+        <v>21.9665</v>
       </c>
       <c r="K13" t="n">
-        <v>5.255</v>
+        <v>16.0967</v>
       </c>
       <c r="L13" t="n">
-        <v>14.6144</v>
+        <v>5.8699</v>
       </c>
       <c r="M13" t="n">
-        <v>-15.5606</v>
+        <v>-28.7972</v>
       </c>
       <c r="N13" t="n">
-        <v>-8.437799999999999</v>
+        <v>-18.4742</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.1226</v>
+        <v>-10.3234</v>
       </c>
       <c r="P13" t="n">
-        <v>8.1272</v>
+        <v>2.1803</v>
       </c>
       <c r="Q13" t="n">
-        <v>-8.9199</v>
+        <v>-32.9047</v>
       </c>
       <c r="R13" t="n">
-        <v>17.0471</v>
+        <v>35.0853</v>
       </c>
       <c r="S13" t="n">
-        <v>-14.1211</v>
+        <v>1.4185</v>
       </c>
       <c r="T13" t="n">
-        <v>-8.9519</v>
+        <v>-4.5401</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.1695</v>
+        <v>5.9587</v>
       </c>
       <c r="V13" t="n">
-        <v>-9.358000000000001</v>
+        <v>-9.5745</v>
       </c>
       <c r="W13" t="n">
-        <v>3.6766</v>
+        <v>13.3185</v>
       </c>
       <c r="X13" t="n">
-        <v>-13.0347</v>
+        <v>-22.8929</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F. SERRANO RUBIO</t>
+          <t>D. WRIGHT RODRIGUEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D14" t="n">
-        <v>-15.8354</v>
+        <v>-13.2603</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.347300000000001</v>
+        <v>-10.4816</v>
       </c>
       <c r="F14" t="n">
-        <v>-10.4882</v>
+        <v>-2.778799999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-6.830699999999999</v>
+        <v>8.9924</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.3772</v>
+        <v>1.0792</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.453499999999999</v>
+        <v>7.912999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>21.9665</v>
+        <v>25.7403</v>
       </c>
       <c r="K14" t="n">
-        <v>16.0967</v>
+        <v>12.7991</v>
       </c>
       <c r="L14" t="n">
-        <v>5.8699</v>
+        <v>12.9412</v>
       </c>
       <c r="M14" t="n">
-        <v>-28.7972</v>
+        <v>-16.7478</v>
       </c>
       <c r="N14" t="n">
-        <v>-18.4742</v>
+        <v>-11.7197</v>
       </c>
       <c r="O14" t="n">
-        <v>-10.3234</v>
+        <v>-5.0284</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1803</v>
+        <v>-8.1272</v>
       </c>
       <c r="Q14" t="n">
-        <v>-32.9047</v>
+        <v>-35.4818</v>
       </c>
       <c r="R14" t="n">
-        <v>35.0853</v>
+        <v>27.3548</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6105</v>
+        <v>6.9921</v>
       </c>
       <c r="T14" t="n">
-        <v>-7.7274</v>
+        <v>1.3826</v>
       </c>
       <c r="U14" t="n">
-        <v>6.116899999999999</v>
+        <v>5.6092</v>
       </c>
       <c r="V14" t="n">
-        <v>-9.5745</v>
+        <v>-21.1175</v>
       </c>
       <c r="W14" t="n">
-        <v>13.3185</v>
+        <v>-2.1225</v>
       </c>
       <c r="X14" t="n">
-        <v>-22.8929</v>
+        <v>-18.995</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. PEREIRA FERNANDES</t>
+          <t>M. VIGO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>-22.7288</v>
+        <v>-17.0616</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7795000000000002</v>
+        <v>-7.0932</v>
       </c>
       <c r="F15" t="n">
-        <v>-23.5081</v>
+        <v>-9.9681</v>
       </c>
       <c r="G15" t="n">
-        <v>-9.909799999999999</v>
+        <v>-17.6166</v>
       </c>
       <c r="H15" t="n">
-        <v>-5.712999999999999</v>
+        <v>2.324800000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-4.1971</v>
+        <v>-19.941</v>
       </c>
       <c r="J15" t="n">
-        <v>28.8454</v>
+        <v>19.9969</v>
       </c>
       <c r="K15" t="n">
-        <v>25.3678</v>
+        <v>28.3876</v>
       </c>
       <c r="L15" t="n">
-        <v>3.4775</v>
+        <v>-8.3904</v>
       </c>
       <c r="M15" t="n">
-        <v>-38.7551</v>
+        <v>-37.6139</v>
       </c>
       <c r="N15" t="n">
-        <v>-31.0809</v>
+        <v>-26.063</v>
       </c>
       <c r="O15" t="n">
-        <v>-7.6742</v>
+        <v>-11.5503</v>
       </c>
       <c r="P15" t="n">
-        <v>13.4794</v>
+        <v>1.1892</v>
       </c>
       <c r="Q15" t="n">
-        <v>-33.1029</v>
+        <v>-46.7805</v>
       </c>
       <c r="R15" t="n">
-        <v>46.5824</v>
+        <v>47.97</v>
       </c>
       <c r="S15" t="n">
-        <v>-3.2089</v>
+        <v>-1.3204</v>
       </c>
       <c r="T15" t="n">
-        <v>-7.3559</v>
+        <v>-0.5187000000000002</v>
       </c>
       <c r="U15" t="n">
-        <v>4.1467</v>
+        <v>-0.8013999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>-23.0892</v>
+        <v>0.6862000000000007</v>
       </c>
       <c r="W15" t="n">
-        <v>12.3931</v>
+        <v>20.209</v>
       </c>
       <c r="X15" t="n">
-        <v>-35.4822</v>
+        <v>-19.5229</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. PEREZ GARCIA</t>
+          <t>R. PEREIRA FERNANDES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-27.1242</v>
+        <v>-19.4084</v>
       </c>
       <c r="E16" t="n">
-        <v>-5.1466</v>
+        <v>4.7255</v>
       </c>
       <c r="F16" t="n">
-        <v>-21.9778</v>
+        <v>-24.1339</v>
       </c>
       <c r="G16" t="n">
-        <v>-9.501799999999999</v>
+        <v>-9.909799999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.4828</v>
+        <v>-5.712999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-8.019099999999998</v>
+        <v>-4.1971</v>
       </c>
       <c r="J16" t="n">
-        <v>19.7337</v>
+        <v>28.8454</v>
       </c>
       <c r="K16" t="n">
-        <v>15.3282</v>
+        <v>25.3678</v>
       </c>
       <c r="L16" t="n">
-        <v>4.4053</v>
+        <v>3.4775</v>
       </c>
       <c r="M16" t="n">
-        <v>-29.2354</v>
+        <v>-38.7551</v>
       </c>
       <c r="N16" t="n">
-        <v>-16.8111</v>
+        <v>-31.0809</v>
       </c>
       <c r="O16" t="n">
-        <v>-12.4244</v>
+        <v>-7.6742</v>
       </c>
       <c r="P16" t="n">
-        <v>-7.928999999999999</v>
+        <v>13.4794</v>
       </c>
       <c r="Q16" t="n">
-        <v>-32.3103</v>
+        <v>-33.1029</v>
       </c>
       <c r="R16" t="n">
-        <v>24.3814</v>
+        <v>46.5824</v>
       </c>
       <c r="S16" t="n">
-        <v>-4.6739</v>
+        <v>0.1111000000000003</v>
       </c>
       <c r="T16" t="n">
-        <v>-2.1967</v>
+        <v>-3.4095</v>
       </c>
       <c r="U16" t="n">
-        <v>-2.4773</v>
+        <v>3.5205</v>
       </c>
       <c r="V16" t="n">
-        <v>-5.0195</v>
+        <v>-23.0892</v>
       </c>
       <c r="W16" t="n">
-        <v>9.626700000000001</v>
+        <v>12.3931</v>
       </c>
       <c r="X16" t="n">
-        <v>-14.6463</v>
+        <v>-35.4822</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. VIGO RODRIGUEZ</t>
+          <t>A. PEREZ GARCIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>-34.9446</v>
+        <v>-23.7637</v>
       </c>
       <c r="E17" t="n">
-        <v>-16.195</v>
+        <v>-3.5038</v>
       </c>
       <c r="F17" t="n">
-        <v>-18.7493</v>
+        <v>-20.2597</v>
       </c>
       <c r="G17" t="n">
-        <v>-17.6166</v>
+        <v>-9.501799999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>2.324800000000001</v>
+        <v>-1.4828</v>
       </c>
       <c r="I17" t="n">
-        <v>-19.941</v>
+        <v>-8.019099999999998</v>
       </c>
       <c r="J17" t="n">
-        <v>19.9969</v>
+        <v>19.7337</v>
       </c>
       <c r="K17" t="n">
-        <v>28.3876</v>
+        <v>15.3282</v>
       </c>
       <c r="L17" t="n">
-        <v>-8.3904</v>
+        <v>4.4053</v>
       </c>
       <c r="M17" t="n">
-        <v>-37.6139</v>
+        <v>-29.2354</v>
       </c>
       <c r="N17" t="n">
-        <v>-26.063</v>
+        <v>-16.8111</v>
       </c>
       <c r="O17" t="n">
-        <v>-11.5503</v>
+        <v>-12.4244</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1892</v>
+        <v>-7.928999999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>-46.7805</v>
+        <v>-32.3103</v>
       </c>
       <c r="R17" t="n">
-        <v>47.97</v>
+        <v>24.3814</v>
       </c>
       <c r="S17" t="n">
-        <v>-19.2032</v>
+        <v>-1.3132</v>
       </c>
       <c r="T17" t="n">
-        <v>-9.620600000000001</v>
+        <v>-0.5539000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-9.5824</v>
+        <v>-0.7591</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6862000000000007</v>
+        <v>-5.0195</v>
       </c>
       <c r="W17" t="n">
-        <v>20.209</v>
+        <v>9.626700000000001</v>
       </c>
       <c r="X17" t="n">
-        <v>-19.5229</v>
+        <v>-14.6463</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>25</v>
       </c>
       <c r="D18" t="n">
-        <v>-53.6499</v>
+        <v>-46.7369</v>
       </c>
       <c r="E18" t="n">
-        <v>-36.9496</v>
+        <v>-33.5191</v>
       </c>
       <c r="F18" t="n">
-        <v>-16.6999</v>
+        <v>-13.2178</v>
       </c>
       <c r="G18" t="n">
         <v>-15.38</v>
@@ -1858,13 +1858,13 @@
         <v>20.6149</v>
       </c>
       <c r="S18" t="n">
-        <v>-7.8792</v>
+        <v>-0.9661999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-4.9761</v>
+        <v>-1.5458</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.9032</v>
+        <v>0.5793</v>
       </c>
       <c r="V18" t="n">
         <v>-10.9645</v>
@@ -1891,13 +1891,13 @@
         <v>19</v>
       </c>
       <c r="D19" t="n">
-        <v>-67.84910000000001</v>
+        <v>-59.5826</v>
       </c>
       <c r="E19" t="n">
-        <v>-71.1605</v>
+        <v>-64.9731</v>
       </c>
       <c r="F19" t="n">
-        <v>3.311599999999999</v>
+        <v>5.3908</v>
       </c>
       <c r="G19" t="n">
         <v>-40.6145</v>
@@ -1936,13 +1936,13 @@
         <v>36.0765</v>
       </c>
       <c r="S19" t="n">
-        <v>-6.503</v>
+        <v>1.7637</v>
       </c>
       <c r="T19" t="n">
-        <v>-9.438000000000001</v>
+        <v>-3.2506</v>
       </c>
       <c r="U19" t="n">
-        <v>2.9351</v>
+        <v>5.0144</v>
       </c>
       <c r="V19" t="n">
         <v>16.7327</v>
@@ -1969,16 +1969,16 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>-126.4978</v>
+        <v>-107.6196</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.035200000000017</v>
+        <v>2.891999999999982</v>
       </c>
       <c r="F20" t="n">
-        <v>-123.4625</v>
+        <v>-110.5114</v>
       </c>
       <c r="G20" t="n">
-        <v>22.87520000000001</v>
+        <v>22.8752</v>
       </c>
       <c r="H20" t="n">
         <v>-11.4475</v>
@@ -2002,25 +2002,25 @@
         <v>-195.4152</v>
       </c>
       <c r="O20" t="n">
-        <v>-85.5245</v>
+        <v>-85.52450000000002</v>
       </c>
       <c r="P20" t="n">
         <v>-74.33430000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>-427.1686999999999</v>
+        <v>-427.1687</v>
       </c>
       <c r="R20" t="n">
-        <v>352.8360999999999</v>
+        <v>352.8361</v>
       </c>
       <c r="S20" t="n">
-        <v>6.4971</v>
+        <v>25.3751</v>
       </c>
       <c r="T20" t="n">
-        <v>-8.996600000000001</v>
+        <v>-3.068899999999998</v>
       </c>
       <c r="U20" t="n">
-        <v>15.4928</v>
+        <v>28.4433</v>
       </c>
       <c r="V20" t="n">
         <v>-81.5348</v>
